--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136042733</v>
       </c>
       <c r="B4" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135791321</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135791318</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136042773</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136042774</v>
       </c>
       <c r="B8" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136042722</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>135791297</v>
       </c>
       <c r="B10" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135791321</v>
+        <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93366</v>
+        <v>93370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,26 +1044,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373025</v>
+        <v>373028</v>
       </c>
       <c r="R5" t="n">
-        <v>6849824</v>
+        <v>6849816</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,27 +1102,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,16 +1148,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135791321</t>
+          <t>https://artportalen.se/Sighting/136347676</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135791318</v>
+        <v>135791321</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>373030</v>
+        <v>373025</v>
       </c>
       <c r="R6" t="n">
-        <v>6849823</v>
+        <v>6849824</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1269,13 +1269,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135791318</t>
+          <t>https://artportalen.se/Sighting/135791321</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136042773</v>
+        <v>136347735</v>
       </c>
       <c r="B7" t="n">
         <v>93372</v>
@@ -1286,26 +1286,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>373352</v>
+        <v>373212</v>
       </c>
       <c r="R7" t="n">
-        <v>6849842</v>
+        <v>6849755</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,27 +1344,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,13 +1390,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042773</t>
+          <t>https://artportalen.se/Sighting/136347735</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136042774</v>
+        <v>135791318</v>
       </c>
       <c r="B8" t="n">
         <v>93372</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>373344</v>
+        <v>373030</v>
       </c>
       <c r="R8" t="n">
-        <v>6849836</v>
+        <v>6849823</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,22 +1465,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1511,16 +1511,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042774</t>
+          <t>https://artportalen.se/Sighting/135791318</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136042722</v>
+        <v>136042773</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>93372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,26 +1528,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373481</v>
+        <v>373352</v>
       </c>
       <c r="R9" t="n">
-        <v>6849815</v>
+        <v>6849842</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1632,43 +1632,43 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042722</t>
+          <t>https://artportalen.se/Sighting/136042773</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135791297</v>
+        <v>136042774</v>
       </c>
       <c r="B10" t="n">
-        <v>98171</v>
+        <v>93372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373550</v>
+        <v>373344</v>
       </c>
       <c r="R10" t="n">
-        <v>6849899</v>
+        <v>6849836</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,22 +1707,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1753,66 +1753,58 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135791297</t>
+          <t>https://artportalen.se/Sighting/136042774</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101156048</v>
+        <v>136347713</v>
       </c>
       <c r="B11" t="n">
-        <v>104628</v>
+        <v>93378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fulan, Dlr</t>
+          <t>Strömsillret, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372862</v>
+        <v>373101</v>
       </c>
       <c r="R11" t="n">
-        <v>6849627</v>
+        <v>6849821</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1836,12 +1828,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,23 +1857,621 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136347713</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136347664</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93390</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>373108</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6849743</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136347664</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136042722</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>373481</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6849815</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042722</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135791297</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98171</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>373550</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6849899</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791297</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136347671</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98182</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>373236</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6849844</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136347671</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>101156048</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fulan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>372862</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6849627</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/101156048</t>
         </is>
@@ -1884,6 +2489,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136042733</v>
       </c>
       <c r="B4" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135791321</v>
       </c>
       <c r="B6" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135791318</v>
       </c>
       <c r="B8" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136042773</v>
       </c>
       <c r="B9" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136042774</v>
       </c>
       <c r="B10" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135791297</v>
       </c>
       <c r="B14" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136042733</v>
       </c>
       <c r="B4" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135791321</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135791318</v>
       </c>
       <c r="B8" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136042773</v>
       </c>
       <c r="B9" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136042774</v>
       </c>
       <c r="B10" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136347713</v>
       </c>
       <c r="B11" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136347664</v>
       </c>
       <c r="B12" t="n">
-        <v>93390</v>
+        <v>93397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136042722</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135791297</v>
       </c>
       <c r="B14" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136347671</v>
       </c>
       <c r="B15" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>135791321</v>
       </c>
       <c r="B6" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135791318</v>
       </c>
       <c r="B8" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136042773</v>
       </c>
       <c r="B9" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136042774</v>
       </c>
       <c r="B10" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136347713</v>
       </c>
       <c r="B11" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136347664</v>
       </c>
       <c r="B12" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>135791297</v>
       </c>
       <c r="B14" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136347671</v>
       </c>
       <c r="B15" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136042733</v>
       </c>
       <c r="B4" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136042773</v>
       </c>
       <c r="B9" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136042774</v>
       </c>
       <c r="B10" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136347713</v>
       </c>
       <c r="B11" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136347664</v>
       </c>
       <c r="B12" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136042722</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136347671</v>
       </c>
       <c r="B15" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135791318</v>
+        <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>93393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>373030</v>
+        <v>373072</v>
       </c>
       <c r="R8" t="n">
-        <v>6849823</v>
+        <v>6849784</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,22 +1465,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1511,16 +1511,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135791318</t>
+          <t>https://artportalen.se/Sighting/136481039</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136042773</v>
+        <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93399</v>
+        <v>93393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,26 +1528,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>373352</v>
+        <v>372884</v>
       </c>
       <c r="R9" t="n">
-        <v>6849842</v>
+        <v>6850001</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,22 +1586,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1632,16 +1632,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042773</t>
+          <t>https://artportalen.se/Sighting/136481040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136042774</v>
+        <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93399</v>
+        <v>93393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,26 +1649,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>373344</v>
+        <v>373235</v>
       </c>
       <c r="R10" t="n">
-        <v>6849836</v>
+        <v>6849844</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,22 +1707,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1753,16 +1753,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042774</t>
+          <t>https://artportalen.se/Sighting/136481261</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136347713</v>
+        <v>135791318</v>
       </c>
       <c r="B11" t="n">
-        <v>93399</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>373101</v>
+        <v>373030</v>
       </c>
       <c r="R11" t="n">
-        <v>6849821</v>
+        <v>6849823</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,27 +1828,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,16 +1874,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136347713</t>
+          <t>https://artportalen.se/Sighting/135791318</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136347664</v>
+        <v>136042773</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>373108</v>
+        <v>373352</v>
       </c>
       <c r="R12" t="n">
-        <v>6849743</v>
+        <v>6849842</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1949,27 +1949,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,16 +1995,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136347664</t>
+          <t>https://artportalen.se/Sighting/136042773</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136042722</v>
+        <v>136042774</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>93399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,26 +2012,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>373481</v>
+        <v>373344</v>
       </c>
       <c r="R13" t="n">
-        <v>6849815</v>
+        <v>6849836</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2116,38 +2116,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042722</t>
+          <t>https://artportalen.se/Sighting/136042774</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135791297</v>
+        <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>98196</v>
+        <v>93399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>373550</v>
+        <v>373101</v>
       </c>
       <c r="R14" t="n">
-        <v>6849899</v>
+        <v>6849821</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2191,27 +2191,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,43 +2237,43 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135791297</t>
+          <t>https://artportalen.se/Sighting/136347713</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136347671</v>
+        <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>98209</v>
+        <v>93399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>373236</v>
+        <v>373073</v>
       </c>
       <c r="R15" t="n">
-        <v>6849844</v>
+        <v>6849786</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,66 +2358,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136347671</t>
+          <t>https://artportalen.se/Sighting/136481021</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101156048</v>
+        <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>104628</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fulan, Dlr</t>
+          <t>Strömsillret, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372862</v>
+        <v>373108</v>
       </c>
       <c r="R16" t="n">
-        <v>6849627</v>
+        <v>6849743</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2441,12 +2433,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2455,25 +2462,986 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136347664</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136480962</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>372873</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6849975</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480962</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136481221</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93437</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>373014</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6849833</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136481221</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136480991</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79230</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>373037</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6850053</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480991</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136042722</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>373481</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6849815</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042722</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135791297</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98196</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>373550</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6849899</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791297</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136347671</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98209</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>373236</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6849844</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136347671</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>101156048</v>
+      </c>
+      <c r="B23" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fulan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>372862</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6849627</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/101156048</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136480977</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79231</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>372891</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6850062</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480977</t>
         </is>
       </c>
     </row>
@@ -2494,6 +3462,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36032-2026 artfynd.xlsx
+++ b/artfynd/A 36032-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136042733</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347676</v>
       </c>
       <c r="B5" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136347735</v>
       </c>
       <c r="B7" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>136481039</v>
       </c>
       <c r="B8" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>136481040</v>
       </c>
       <c r="B9" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136481261</v>
       </c>
       <c r="B10" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136042773</v>
       </c>
       <c r="B12" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>136042774</v>
       </c>
       <c r="B13" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136347713</v>
       </c>
       <c r="B14" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136481021</v>
       </c>
       <c r="B15" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>136347664</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136480962</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>136481221</v>
       </c>
       <c r="B18" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>136480991</v>
       </c>
       <c r="B19" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136347671</v>
       </c>
       <c r="B22" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>136480977</v>
       </c>
       <c r="B24" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
